--- a/daily_matches/job_matches_2026-04-24.xlsx
+++ b/daily_matches/job_matches_2026-04-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Robert E. Mason &amp; Associates</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, FAISS, Prompt Engineering, PyTorch, Redshift, FastAPI, Docker</t>
+          <t>RAG, S3, Glue, Athena, Data Lake, Kinesis, CI/CD, Git, Snowflake, PySpark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=841c5d40dc8dd444</t>
+          <t>https://www.indeed.com/viewjob?jk=92ccc9ae466ace7c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Operator / Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>East Harbor</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Git, NoSQL, Python, SQL</t>
+          <t>RAG, CI/CD, Terraform, Git, Databricks, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,59 +531,59 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba9dbe2198fbe39a</t>
+          <t>https://www.indeed.com/viewjob?jk=21e2d7ded8a6f7c6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST I</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Central Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, YOLO, Glue, Redshift, Snowflake, Redshift, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Data Lake, CI/CD, GitHub Actions, Git, Snowflake, Kafka, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1133298756b1fd23</t>
+          <t>https://www.indeed.com/viewjob?jk=326c78111f5647b3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Associate Business Systems Analyst</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Upstart</t>
+          <t>Wolters Kluwer</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,52 +591,192 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Matplotlib, Python, SQL, R, Scala, Hypothesis Testing, A/B Testing</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14474a4ec1e81991</t>
+          <t>https://www.indeed.com/viewjob?jk=91578e8aca97956e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Sr Analyst, Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, CI/CD, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c7fa499115c857a</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>DevOps Engineer (Kubernetes)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>FICO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Kubernetes, CI/CD, Terraform, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c51c122a84f5b72b</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Data Scientist 2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Baylor Scott &amp; White Health</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, Snowflake, Databricks, PySpark, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4f2f747ca11eaff</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sr Quality Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Fiserv</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>King of Prussia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>10</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>CI/CD, Terraform, Git, NoSQL, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e7e1336575ef22</t>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=624edd1fd063e9a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sr Quality Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Fiserv</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>King of Prussia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03175b5df9f9008e</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-24.xlsx
+++ b/daily_matches/job_matches_2026-04-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
+          <t>Forward Deployed AI Engineer, TechEx, Software -US</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Data Lake, Kinesis, CI/CD, Git, Snowflake, PySpark</t>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,102 +496,102 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92ccc9ae466ace7c</t>
+          <t>https://www.indeed.com/viewjob?jk=60f2fb7ebcf41f56</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Terraform, Git, Databricks, NoSQL, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, XGBoost, AWS SageMaker, S3, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21e2d7ded8a6f7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=65d630f1de857722</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>Java API Gateway Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Central Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, CI/CD, GitHub Actions, Git, Snowflake, Kafka, SQL, R</t>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=326c78111f5647b3</t>
+          <t>https://www.indeed.com/viewjob?jk=825e1da1e53f7539</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Associate Business Systems Analyst</t>
+          <t>Java API Gateway Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wolters Kluwer</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, Git, Python, SQL, R, Java</t>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,182 +601,567 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91578e8aca97956e</t>
+          <t>https://www.indeed.com/viewjob?jk=0615a052696ffb78</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr Analyst, Data Engineer</t>
+          <t>Application Scientist - Digital Pathology</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, OpenCV, S3, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c7fa499115c857a</t>
+          <t>https://www.indeed.com/viewjob?jk=249f2368c59e1e5a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Kubernetes)</t>
+          <t>Distinguished Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Kubernetes, CI/CD, Terraform, Git, Python, R, Optimization</t>
+          <t>RAG, S3, Glue, Kinesis, Terraform, Snowflake, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c51c122a84f5b72b</t>
+          <t>https://www.indeed.com/viewjob?jk=4b1beaee3c6388b3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Scientist 2</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Baylor Scott &amp; White Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Snowflake, Databricks, PySpark, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, MongoDB, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f2f747ca11eaff</t>
+          <t>https://www.indeed.com/viewjob?jk=9596f31813ea3f9b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Quality Engineer</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=624edd1fd063e9a2</t>
+          <t>https://www.indeed.com/viewjob?jk=cc188fef3c972dfb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Quality Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Generative AI, LLaMA, TensorFlow, PyTorch, Docker, CI/CD, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1aef6da600c71bb6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Java Trainer / Mentor / Educator</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f4b4871bab6bff0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Generative AI, LLaMA, TensorFlow, PyTorch, Docker, CI/CD, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da2c0daf1aaa4429</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Event Streaming Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BDIPlus</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, S3, Glue, Athena, Terraform, Kafka, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d7d7d17e07dc955</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SQL/ETL Developer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>FULLTHROTTLE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, Keras, spaCy, NLTK, OpenCV, S3, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c80ee59a9e4fa6ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BDIPlus</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, S3, Glue, Athena, Data Lake, FastAPI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84f981cdc4f485cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - AI (.Net)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Momentive Software</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e0e60e511e179411</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Software Engineer II - AI (.Net)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Momentive Software</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=585911ed91b1cb6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>10</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AI Engineer, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4d27494427cbf48</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, MLflow, Databricks, Hadoop, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8325825d701390f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Engineer Senior</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Acuity Inc.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, FastAPI, Kubernetes, CI/CD, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=03175b5df9f9008e</t>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d5885bd7476fae7</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Caris Life Sciences</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, CI/CD, PostgreSQL, MySQL, MongoDB, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=41257a5482aea623</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-24.xlsx
+++ b/daily_matches/job_matches_2026-04-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Forward Deployed AI Engineer, TechEx, Software -US</t>
+          <t>Engineer, Software</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Calabrio</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Snowflake, Databricks</t>
+          <t>S3, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f2fb7ebcf41f56</t>
+          <t>https://www.indeed.com/viewjob?jk=5f67526228c2d8ea</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Python Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, XGBoost, AWS SageMaker, S3, MLflow, Docker, Kubernetes</t>
+          <t>EC2, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65d630f1de857722</t>
+          <t>https://www.indeed.com/viewjob?jk=a8243a564207213c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Java API Gateway Developer</t>
+          <t>Development Operations Engineer I</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>University of Alabama</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tuscaloosa, AL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RAG, BigQuery, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=825e1da1e53f7539</t>
+          <t>https://www.indeed.com/viewjob?jk=94077e631f4537b0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Java API Gateway Developer</t>
+          <t>Development Operations Engineer I</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>University of Alabama</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tuscaloosa, AL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RAG, BigQuery, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,567 +601,42 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0615a052696ffb78</t>
+          <t>https://www.indeed.com/viewjob?jk=8d9af03ec88b79f1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Application Scientist - Digital Pathology</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, OpenCV, S3, Docker, Kubernetes, CI/CD, Git</t>
+          <t>RAG, S3, EC2, Git, MySQL, MongoDB, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=249f2368c59e1e5a</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Distinguished Data Engineer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>RAG, S3, Glue, Kinesis, Terraform, Snowflake, Databricks, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b1beaee3c6388b3</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Java CI/CD Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, MongoDB, NoSQL, SQL, R</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9596f31813ea3f9b</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Java Trainer / Mentor / Educator</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cc188fef3c972dfb</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Generative AI, LLaMA, TensorFlow, PyTorch, Docker, CI/CD, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1aef6da600c71bb6</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Java Trainer / Mentor / Educator</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4b4871bab6bff0</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Generative AI, LLaMA, TensorFlow, PyTorch, Docker, CI/CD, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da2c0daf1aaa4429</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior Event Streaming Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>BDIPlus</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, S3, Glue, Athena, Terraform, Kafka, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d7d7d17e07dc955</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>SQL/ETL Developer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>FULLTHROTTLE</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>TensorFlow, PyTorch, Keras, spaCy, NLTK, OpenCV, S3, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c80ee59a9e4fa6ba</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>BDIPlus</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, S3, Glue, Athena, Data Lake, FastAPI, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=84f981cdc4f485cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - AI (.Net)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Momentive Software</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e60e511e179411</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Software Engineer II - AI (.Net)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Momentive Software</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=585911ed91b1cb6d</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>AI Integration Engineer (Java + AI)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>AI Engineer, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d27494427cbf48</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Data Scientist, TensorFlow, PyTorch, MLflow, Databricks, Hadoop, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8325825d701390f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Software Engineer Senior</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Acuity Inc.</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, FastAPI, Kubernetes, CI/CD, NoSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5885bd7476fae7</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Caris Life Sciences</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Data Scientist, CI/CD, PostgreSQL, MySQL, MongoDB, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=41257a5482aea623</t>
+          <t>https://www.indeed.com/viewjob?jk=995dfe3cc7599f4e</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-24.xlsx
+++ b/daily_matches/job_matches_2026-04-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Engineer, Software</t>
+          <t>ML Engineering Consultant</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Calabrio</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>S3, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MongoDB</t>
+          <t>Data Scientist, Machine Learning Engineer, LangChain, TensorFlow, PyTorch, XGBoost, MLflow, Docker, Kubernetes, Apache Airflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f67526228c2d8ea</t>
+          <t>https://www.indeed.com/viewjob?jk=3af99e279232368b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Python Software Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>BridgeNexus Technologies Inc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>21.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>EC2, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8243a564207213c</t>
+          <t>https://www.indeed.com/viewjob?jk=8b141076859f8d17</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Development Operations Engineer I</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>University of Alabama</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tuscaloosa, AL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, XGBoost, AWS SageMaker, S3, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94077e631f4537b0</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd13d9bc2495c26</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Development Operations Engineer I</t>
+          <t>Machine Learning &amp; Operations Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>University of Alabama</t>
+          <t>OptiTrack</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tuscaloosa, AL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery, Python</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, Docker, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,42 +601,707 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d9af03ec88b79f1</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc79b80048fb6a0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Machine Learning &amp; Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>OptiTrack</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, Docker, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c39760b84f3ba19b</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Machine Learning &amp; Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>OptiTrack</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Corvallis, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, Docker, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b491b874fd82c8cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Two Six Technologies</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24bb5555b339ec54</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - APIs</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>HCA Healthcare</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Dataflow, Kubernetes, CI/CD, Git, BigQuery, Kafka, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=40caa2125a3057cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AI, Data &amp; Technology - AI-ML Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Grant Thornton</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, XGBoost, BigQuery, CI/CD, Snowflake, Databricks, BigQuery, Python</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=95573df7935ae886</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Automation</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Trinity Logistics</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Seaford, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Copilot, S3, Docker, Kubernetes, Terraform, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1fe28a5e43309328</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, S3, EC2, Python, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6d9aaad9a392e2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Java CI/CD Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, MongoDB, NoSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a379816f2d21d13</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Generative AI, LLaMA, TensorFlow, PyTorch, Docker, CI/CD, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e0bc90008362813</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Java Trainer / Mentor / Educator</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, EC2, Data Lake, Kubernetes, CI/CD, Kafka, NoSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa91f0490d487d6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Java Trainer / Mentor / Educator</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, EC2, Data Lake, Kubernetes, CI/CD, Kafka, NoSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1acc4fe9bbc488ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Canopy Tax</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Tableau, Matplotlib, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a348df1cbb42bd5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AI Model Deployment Administrator</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, FAISS, Pinecone, Prompt Engineering, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad0cc5c30e360e6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>DevOps Engineer Mobile</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Air Apps</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=28d1f3ba8d07b97e</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ground Data Software Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Lockheed Martin</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Littleton, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Dataflow, Git, Hadoop, MySQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f69b94e4061cbd5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Senior Software Engineer</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Zoom Communications</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>RAG, S3, EC2, Git, MySQL, MongoDB, NoSQL, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=995dfe3cc7599f4e</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ithaka</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Databricks, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8050e528f6abd803</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AI Model Deployment Administrator</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Copilot, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cecb379f26097242</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AI Model Deployment Administrator</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Gemini, Copilot, Prompt Engineering, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76590de2e1d5f299</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, MLflow, Databricks, Hadoop, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=440de4a0b98cfdc3</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Thrivent</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Git, Kafka, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2fc85a5c8ab7016</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-24.xlsx
+++ b/daily_matches/job_matches_2026-04-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ML Engineering Consultant</t>
+          <t>Multi-Cloud Engineer - SQL Database (DBA) Focused</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>14.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, LangChain, TensorFlow, PyTorch, XGBoost, MLflow, Docker, Kubernetes, Apache Airflow</t>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af99e279232368b</t>
+          <t>https://www.indeed.com/viewjob?jk=cd9af1111f848535</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Backend Engineer (Infrastructure &amp; DevOps Focus)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BridgeNexus Technologies Inc</t>
+          <t>Bedrock Data</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b141076859f8d17</t>
+          <t>https://www.indeed.com/viewjob?jk=417e75279c31d7ca</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, XGBoost, AWS SageMaker, S3, MLflow, Docker, Kubernetes</t>
+          <t>Generative AI, Docker, Kubernetes, Jenkins, Terraform, Git, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd13d9bc2495c26</t>
+          <t>https://www.indeed.com/viewjob?jk=f72b719cfa087347</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, Docker, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Generative AI, Docker, Kubernetes, Jenkins, Terraform, Git, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc79b80048fb6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=f1957453af9e455e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Site Reliability Engineer (SRE) – II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, Docker, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39760b84f3ba19b</t>
+          <t>https://www.indeed.com/viewjob?jk=4c307a35b1d669fd</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Operations Engineer</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OptiTrack</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Corvallis, OR, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, Docker, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Data Scientist, Generative AI, RAG, Git, Cassandra, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b491b874fd82c8cc</t>
+          <t>https://www.indeed.com/viewjob?jk=90db224d9a488735</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Two Six Technologies</t>
+          <t>Twin Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, Git, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24bb5555b339ec54</t>
+          <t>https://www.indeed.com/viewjob?jk=0d4253ce92658799</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Dataflow, Kubernetes, CI/CD, Git, BigQuery, Kafka, Python, SQL</t>
+          <t>RAG, BigQuery, Kinesis, Docker, Kubernetes, CI/CD, BigQuery, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40caa2125a3057cc</t>
+          <t>https://www.indeed.com/viewjob?jk=1da9309099e24717</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI, Data &amp; Technology - AI-ML Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Grant Thornton</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, XGBoost, BigQuery, CI/CD, Snowflake, Databricks, BigQuery, Python</t>
+          <t>RAG, BigQuery, Kinesis, Docker, Kubernetes, CI/CD, BigQuery, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95573df7935ae886</t>
+          <t>https://www.indeed.com/viewjob?jk=eb9f7f7de61a86fc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Automation</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Trinity Logistics</t>
+          <t>PrizePicks</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Seaford, DE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Copilot, S3, Docker, Kubernetes, Terraform, Git, Python, SQL, R, Java</t>
+          <t>RAG, BigQuery, Kinesis, Docker, Kubernetes, CI/CD, BigQuery, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fe28a5e43309328</t>
+          <t>https://www.indeed.com/viewjob?jk=838858c3ed703639</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Generative &amp; Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, S3, EC2, Python, R</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6d9aaad9a392e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=479b9625a783d6d4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>Conversational AI Developer with NLP</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, MongoDB, NoSQL, SQL, R</t>
+          <t>NLP Engineer, TensorFlow, PyTorch, spaCy, Git, MongoDB, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a379816f2d21d13</t>
+          <t>https://www.indeed.com/viewjob?jk=29d5d228ad4af978</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Chess.com</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, LLaMA, TensorFlow, PyTorch, Docker, CI/CD, Git, Python, SQL, R</t>
+          <t>RAG, Kubernetes, Terraform, MySQL, Cassandra, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e0bc90008362813</t>
+          <t>https://www.indeed.com/viewjob?jk=3d957645e55a581d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DomainTools</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, EC2, Data Lake, Kubernetes, CI/CD, Kafka, NoSQL, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, Apache Airflow, Kafka, MySQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa91f0490d487d6f</t>
+          <t>https://www.indeed.com/viewjob?jk=31173ca9dbcd6588</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DomainTools</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, EC2, Data Lake, Kubernetes, CI/CD, Kafka, NoSQL, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, Apache Airflow, Kafka, MySQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1acc4fe9bbc488ff</t>
+          <t>https://www.indeed.com/viewjob?jk=21769fe3b7e50cb4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Canopy Tax</t>
+          <t>DomainTools</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Tableau, Matplotlib, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, Apache Airflow, Kafka, MySQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a348df1cbb42bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=563b2c70fce7fa8d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Model Deployment Administrator</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DomainTools</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, FAISS, Pinecone, Prompt Engineering, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, Apache Airflow, Kafka, MySQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad0cc5c30e360e6c</t>
+          <t>https://www.indeed.com/viewjob?jk=4bff5720c043eab6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DevOps Engineer Mobile</t>
+          <t>Data Analysis Engineer – Structure Simulation</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Air Apps</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Champaign, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, AKS, Git, Snowflake, MySQL, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28d1f3ba8d07b97e</t>
+          <t>https://www.indeed.com/viewjob?jk=21f273d04a7a2ae1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ground Data Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>TTX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Dataflow, Git, Hadoop, MySQL, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Azure ML, Synapse, Data Lake, Power BI, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f69b94e4061cbd5d</t>
+          <t>https://www.indeed.com/viewjob?jk=94c5901292c76d57</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ithaka</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Databricks, Python, SQL, R, Java</t>
+          <t>AI Engineer, Data Scientist, RAG, Databricks, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8050e528f6abd803</t>
+          <t>https://www.indeed.com/viewjob?jk=8f43e5255e894179</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Model Deployment Administrator</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HARVEST GROUP</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cecb379f26097242</t>
+          <t>https://www.indeed.com/viewjob?jk=c17adfb345078a16</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Model Deployment Administrator</t>
+          <t>Senior Systems Administrator</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PingWind Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Gemini, Copilot, Prompt Engineering, Python, R, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76590de2e1d5f299</t>
+          <t>https://www.indeed.com/viewjob?jk=5f9b49582e9c56ae</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Image &amp; Computer Vision AI Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, MLflow, Databricks, Hadoop, Python, R, Java</t>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, OpenCV, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,42 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=440de4a0b98cfdc3</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Thrivent</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Git, Kafka, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c2fc85a5c8ab7016</t>
+          <t>https://www.indeed.com/viewjob?jk=c33b13265d526bf4</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-24.xlsx
+++ b/daily_matches/job_matches_2026-04-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Multi-Cloud Engineer - SQL Database (DBA) Focused</t>
+          <t>Senior Data Engineer - Data &amp; ML Platform</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>oura</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, PostgreSQL, MySQL, NoSQL</t>
+          <t>Data Scientist, RAG, S3, Glue, Athena, Kinesis, Docker, CI/CD, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd9af1111f848535</t>
+          <t>https://www.indeed.com/viewjob?jk=712997349ec8d11d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Backend Engineer (Infrastructure &amp; DevOps Focus)</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedrock Data</t>
+          <t>Medal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, BigQuery, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery, MySQL, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=417e75279c31d7ca</t>
+          <t>https://www.indeed.com/viewjob?jk=c44d2e760ed95d49</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>General Intuition &amp; Medal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, Docker, Kubernetes, Jenkins, Terraform, Git, NoSQL, SQL, R, Java</t>
+          <t>RAG, BigQuery, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery, MySQL, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72b719cfa087347</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd140da724c069c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>AI Testing Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, Docker, Kubernetes, Jenkins, Terraform, Git, NoSQL, SQL, R, Java</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1957453af9e455e</t>
+          <t>https://www.indeed.com/viewjob?jk=e98247ffa20b79b2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) – II</t>
+          <t>Software Engineer, DFIR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Tokio Marine HCC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
+          <t>Kinesis, Kubernetes, Apache Airflow, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c307a35b1d669fd</t>
+          <t>https://www.indeed.com/viewjob?jk=aa30285abbf1788b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>NLP &amp; Scientific Integrity Post-Doc</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Git, Cassandra, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, Hugging Face, PyTorch, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90db224d9a488735</t>
+          <t>https://www.indeed.com/viewjob?jk=6b85ad21805397cf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>NLP &amp; Scientific Integrity Post-Doc</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Twin Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, Git, Snowflake, Python, SQL, R</t>
+          <t>RAG, Copilot, Hugging Face, PyTorch, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d4253ce92658799</t>
+          <t>https://www.indeed.com/viewjob?jk=b88420d58b6bcbdd</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Software Engineer - SRE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Kinesis, Docker, Kubernetes, CI/CD, BigQuery, Kafka, Python, R</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1da9309099e24717</t>
+          <t>https://www.indeed.com/viewjob?jk=21f79af4f138986f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Sr. Development Support Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>Radiology Partners</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Kinesis, Docker, Kubernetes, CI/CD, BigQuery, Kafka, Python, R</t>
+          <t>RAG, EC2, Docker, Kubernetes, CI/CD, Git, Databricks, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb9f7f7de61a86fc</t>
+          <t>https://www.indeed.com/viewjob?jk=1de422c2feb64a45</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PrizePicks</t>
+          <t>RVO Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Kinesis, Docker, Kubernetes, CI/CD, BigQuery, Kafka, Python, R</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Git, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=838858c3ed703639</t>
+          <t>https://www.indeed.com/viewjob?jk=c117fc952b553a1f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Generative &amp; Agentic AI Engineer</t>
+          <t>Sr Cloud Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>Abacus</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Python, R, Optimization</t>
+          <t>Generative AI, Gemini, Copilot, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=479b9625a783d6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=cc9177734e7ea91a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Conversational AI Developer with NLP</t>
+          <t>Sr AI/ML Engineer - Remote Nationwide or Hybrid in MN/DC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>NLP Engineer, TensorFlow, PyTorch, spaCy, Git, MongoDB, Python, R, Java, Scala</t>
+          <t>AI Engineer, LangChain, RAG, Hugging Face, Prompt Engineering, PyTorch, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29d5d228ad4af978</t>
+          <t>https://www.indeed.com/viewjob?jk=87f2f414e466c663</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Sr. Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Chess.com</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Terraform, MySQL, Cassandra, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Data Lake, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d957645e55a581d</t>
+          <t>https://www.indeed.com/viewjob?jk=93dce2213d1e9036</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DomainTools</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Apache Airflow, Kafka, MySQL, SQL, R, Java, Scala</t>
+          <t>RAG, Data Lake, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31173ca9dbcd6588</t>
+          <t>https://www.indeed.com/viewjob?jk=8ecea4039de4e759</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DomainTools</t>
+          <t>NAVEX</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Apache Airflow, Kafka, MySQL, SQL, R, Java, Scala</t>
+          <t>RAG, S3, EC2, Terraform, Git, PostgreSQL, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21769fe3b7e50cb4</t>
+          <t>https://www.indeed.com/viewjob?jk=90d2963f603b34cf</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DomainTools</t>
+          <t>NAVEX</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Apache Airflow, Kafka, MySQL, SQL, R, Java, Scala</t>
+          <t>RAG, S3, EC2, Terraform, Git, PostgreSQL, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563b2c70fce7fa8d</t>
+          <t>https://www.indeed.com/viewjob?jk=ac0daba36fe4f471</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Software Development Engineer III - Agent Platform</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DomainTools</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Apache Airflow, Kafka, MySQL, SQL, R, Java, Scala</t>
+          <t>Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,217 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bff5720c043eab6</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Data Analysis Engineer – Structure Simulation</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Caterpillar</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Champaign, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, AKS, Git, Snowflake, MySQL, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=21f273d04a7a2ae1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>TTX</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Azure ML, Synapse, Data Lake, Power BI, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=94c5901292c76d57</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Genworth</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, RAG, Databricks, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f43e5255e894179</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>HARVEST GROUP</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c17adfb345078a16</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Senior Systems Administrator</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>PingWind Inc.</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, R</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5f9b49582e9c56ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Image &amp; Computer Vision AI Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>hatch IT</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, OpenCV, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c33b13265d526bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=ad27b76209ce20d7</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-24.xlsx
+++ b/daily_matches/job_matches_2026-04-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; ML Platform</t>
+          <t>Cloud AI Consultant</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>oura</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>28.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Glue, Athena, Kinesis, Docker, CI/CD, Snowflake, Databricks</t>
+          <t>RAG, S3, EC2, Redshift, BigQuery, Docker, Kubernetes, AKS, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=712997349ec8d11d</t>
+          <t>https://www.indeed.com/viewjob?jk=5b44724ef07bf0a9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Medal</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Walton Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery, MySQL, SQL</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Glue, Redshift, Apache Airflow, Git, Snowflake, Redshift</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44d2e760ed95d49</t>
+          <t>https://www.indeed.com/viewjob?jk=77ec6df15b6232d2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>AI Engineer - Automated Channels Transformation</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>General Intuition &amp; Medal</t>
+          <t>Fifth Third Bank</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>21.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery, MySQL, SQL</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, PyTorch, Docker</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebd140da724c069c</t>
+          <t>https://www.indeed.com/viewjob?jk=72d8c97aa9a824d5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Testing Architect</t>
+          <t>Senior Polyglot Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>Fanisko</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, CI/CD, Jenkins, GitHub Actions, Git</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, S3, EC2, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e98247ffa20b79b2</t>
+          <t>https://www.indeed.com/viewjob?jk=6e5fe1bc7edc545c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer, DFIR</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tokio Marine HCC</t>
+          <t>Bandwidth</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kinesis, Kubernetes, Apache Airflow, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python, SQL</t>
+          <t>AI Engineer, LangChain, RAG, Pinecone, Prompt Engineering, S3, EC2, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa30285abbf1788b</t>
+          <t>https://www.indeed.com/viewjob?jk=ba5bb4605935b43a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NLP &amp; Scientific Integrity Post-Doc</t>
+          <t>Sr. Business Intelligence Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Hugging Face, PyTorch, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python</t>
+          <t>RAG, Data Lake, CI/CD, GitHub Actions, Git, Snowflake, Databricks, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b85ad21805397cf</t>
+          <t>https://www.indeed.com/viewjob?jk=a7def3d6275f90f3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NLP &amp; Scientific Integrity Post-Doc</t>
+          <t>Sr. Business Intelligence Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Hugging Face, PyTorch, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python</t>
+          <t>RAG, Data Lake, CI/CD, GitHub Actions, Git, Snowflake, Databricks, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88420d58b6bcbdd</t>
+          <t>https://www.indeed.com/viewjob?jk=748e1ac563cf5647</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer - SRE</t>
+          <t>Sr. Engineer, AI &amp; ML</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, Azure ML, MLflow, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21f79af4f138986f</t>
+          <t>https://www.indeed.com/viewjob?jk=49706e226d40254f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Development Support Engineer</t>
+          <t>Sr. Engineer, AI &amp; ML</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Radiology Partners</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, EC2, Docker, Kubernetes, CI/CD, Git, Databricks, NoSQL, Python, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, Azure ML, MLflow, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1de422c2feb64a45</t>
+          <t>https://www.indeed.com/viewjob?jk=af4ea9bc457a6df9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RVO Health</t>
+          <t>10X Genomics</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Git, Python</t>
+          <t>Generative AI, RAG, S3, Data Lake, Docker, Kubernetes, Snowflake, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c117fc952b553a1f</t>
+          <t>https://www.indeed.com/viewjob?jk=ac3f880613f0e9a7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Cloud Architect</t>
+          <t>Compliance - Applied AI/ML Senior Associate</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Abacus</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, Gemini, Copilot, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, RAG, XGBoost, LightGBM, CatBoost, AKS, Git, Databricks, Matplotlib, Seaborn</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc9177734e7ea91a</t>
+          <t>https://www.indeed.com/viewjob?jk=4b0a48359317f88f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr AI/ML Engineer - Remote Nationwide or Hybrid in MN/DC</t>
+          <t>Associate - Data Engineering</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Hugging Face, Prompt Engineering, PyTorch, Python, SQL, R, Scala</t>
+          <t>RAG, Prompt Engineering, FastAPI, Kubernetes, Apache Airflow, Snowflake, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87f2f414e466c663</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fa2510d982dff7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Engineer</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>Hunter Douglas</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Power BI, Python, SQL</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Git, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93dce2213d1e9036</t>
+          <t>https://www.indeed.com/viewjob?jk=464221b9c1ca37ae</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Engineer</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>Hunter Douglas</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Broomfield, CO, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Power BI, Python, SQL</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Git, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ecea4039de4e759</t>
+          <t>https://www.indeed.com/viewjob?jk=c1c37e60286eff77</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Ground Data Software Engineer - Mid-Career - Level 3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NAVEX</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lake Oswego, OR, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Terraform, Git, PostgreSQL, Python, SQL, R, Optimization</t>
+          <t>RAG, S3, Dataflow, Kubernetes, Git, Hadoop, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90d2963f603b34cf</t>
+          <t>https://www.indeed.com/viewjob?jk=568d3ad6a7cfa045</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer III - Gen AI, Java Full stack</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NAVEX</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Terraform, Git, PostgreSQL, Python, SQL, R, Optimization</t>
+          <t>Generative AI, LangChain, RAG, PyTorch, Keras, CI/CD, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,42 +1021,217 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac0daba36fe4f471</t>
+          <t>https://www.indeed.com/viewjob?jk=a76c903a1fee6b7d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Full Stack Software Development Engineer III - Agent Platform</t>
+          <t>Associate Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>Morgantown, WV, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, Prompt Engineering, Docker, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=35769ad87eb1ad10</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Software Engineer II (On-site in office in Jacksonville, FL or Alpharetta, GA))</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Global Payments</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>TensorFlow, Hadoop, MySQL, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b0eefa1c50ab2f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Engineer II (On-site in office in Jacksonville, FL or Alpharetta, GA))</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Global Payments</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>TensorFlow, Hadoop, MySQL, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=effe8c4bc03d18bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Software Engineer II (On-site in office in Jacksonville, FL or Alpharetta, GA))</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Global Payments</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>Atlanta, GA, US USA</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad27b76209ce20d7</t>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>TensorFlow, Hadoop, MySQL, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b29b49ab981155f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist Specialist (Remote)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>US Foods</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Rosemont, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, Data Lake, CI/CD, Git, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fee64d3c26681431</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Sr Data Scientist - Supply Chain</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>The Home Depot</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0d054132000cc3df</t>
         </is>
       </c>
     </row>
